--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC3B40F-21F1-4F1B-B914-4BC7C6C68947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7CAC21-3B5E-4C81-A031-F4170AFCEED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="15285" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8940" yWindow="435" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="157">
   <si>
     <t>ClassName</t>
   </si>
@@ -807,6 +807,14 @@
   </si>
   <si>
     <t>FuncMasterIryoKikan</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncMasterShinryokamoku_DlgEntry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncMasterShinryokamoku</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3596,46 +3604,99 @@
       <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A149" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D149" s="6"/>
+      <c r="E149" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
-      <c r="C150" s="5"/>
+      <c r="A150" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D150" s="6"/>
-      <c r="E150" s="6"/>
+      <c r="E150" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
-      <c r="C151" s="5"/>
+      <c r="A151" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D151" s="6"/>
-      <c r="E151" s="6"/>
+      <c r="E151" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
-      <c r="C152" s="5"/>
+      <c r="A152" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="D152" s="6"/>
-      <c r="E152" s="6"/>
+      <c r="E152" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
-      <c r="C153" s="5"/>
+      <c r="A153" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="D153" s="6"/>
-      <c r="E153" s="6"/>
+      <c r="E153" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
-      <c r="C154" s="5"/>
+      <c r="A154" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D154" s="6"/>
-      <c r="E154" s="6"/>
+      <c r="E154" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B7CAC21-3B5E-4C81-A031-F4170AFCEED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02069992-BCA7-4F09-BA2D-3855102E613B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="435" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$147</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="160">
   <si>
     <t>ClassName</t>
   </si>
@@ -816,6 +816,15 @@
   <si>
     <t>FuncMasterShinryokamoku</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncKaiin</t>
+  </si>
+  <si>
+    <t>FuncKaiin_DlgEntry</t>
+  </si>
+  <si>
+    <t>FuncKaiin_DlgEntry_Idoinfo</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F241"/>
+  <dimension ref="A1:F247"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -3700,67 +3709,131 @@
       <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A155" s="3"/>
-      <c r="B155" s="3"/>
-      <c r="C155" s="5"/>
+      <c r="A155" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>20</v>
+      </c>
       <c r="D155" s="6"/>
-      <c r="E155" s="6"/>
+      <c r="E155" s="6" t="s">
+        <v>23</v>
+      </c>
       <c r="F155" s="4"/>
     </row>
     <row r="156" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
-      <c r="C156" s="5"/>
+      <c r="A156" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="D156" s="6"/>
-      <c r="E156" s="6"/>
+      <c r="E156" s="6" t="s">
+        <v>24</v>
+      </c>
       <c r="F156" s="4"/>
     </row>
     <row r="157" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
-      <c r="C157" s="5"/>
+      <c r="A157" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="D157" s="6"/>
-      <c r="E157" s="6"/>
+      <c r="E157" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="F157" s="4"/>
     </row>
     <row r="158" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
-      <c r="C158" s="5"/>
+      <c r="A158" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D158" s="6"/>
-      <c r="E158" s="6"/>
+      <c r="E158" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F158" s="4"/>
     </row>
     <row r="159" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
-      <c r="C159" s="5"/>
+      <c r="A159" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D159" s="6"/>
-      <c r="E159" s="6"/>
+      <c r="E159" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="F159" s="4"/>
     </row>
     <row r="160" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="5"/>
+      <c r="A160" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D160" s="6"/>
-      <c r="E160" s="6"/>
+      <c r="E160" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F160" s="4"/>
     </row>
     <row r="161" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
-      <c r="C161" s="5"/>
+      <c r="A161" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D161" s="6"/>
-      <c r="E161" s="6"/>
+      <c r="E161" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="F161" s="4"/>
     </row>
     <row r="162" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
-      <c r="C162" s="5"/>
+      <c r="A162" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B162" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D162" s="6"/>
-      <c r="E162" s="6"/>
+      <c r="E162" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F162" s="4"/>
     </row>
     <row r="163" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4394,6 +4467,54 @@
       <c r="D241" s="6"/>
       <c r="E241" s="6"/>
       <c r="F241" s="4"/>
+    </row>
+    <row r="242" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A242" s="3"/>
+      <c r="B242" s="3"/>
+      <c r="C242" s="5"/>
+      <c r="D242" s="6"/>
+      <c r="E242" s="6"/>
+      <c r="F242" s="4"/>
+    </row>
+    <row r="243" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A243" s="3"/>
+      <c r="B243" s="3"/>
+      <c r="C243" s="5"/>
+      <c r="D243" s="6"/>
+      <c r="E243" s="6"/>
+      <c r="F243" s="4"/>
+    </row>
+    <row r="244" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A244" s="3"/>
+      <c r="B244" s="3"/>
+      <c r="C244" s="5"/>
+      <c r="D244" s="6"/>
+      <c r="E244" s="6"/>
+      <c r="F244" s="4"/>
+    </row>
+    <row r="245" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A245" s="3"/>
+      <c r="B245" s="3"/>
+      <c r="C245" s="5"/>
+      <c r="D245" s="6"/>
+      <c r="E245" s="6"/>
+      <c r="F245" s="4"/>
+    </row>
+    <row r="246" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A246" s="3"/>
+      <c r="B246" s="3"/>
+      <c r="C246" s="5"/>
+      <c r="D246" s="6"/>
+      <c r="E246" s="6"/>
+      <c r="F246" s="4"/>
+    </row>
+    <row r="247" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A247" s="3"/>
+      <c r="B247" s="3"/>
+      <c r="C247" s="5"/>
+      <c r="D247" s="6"/>
+      <c r="E247" s="6"/>
+      <c r="F247" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02069992-BCA7-4F09-BA2D-3855102E613B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034335D0-8935-4D28-9124-0DEEC64DEFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="690" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="160">
   <si>
     <t>ClassName</t>
   </si>
@@ -1228,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -3600,31 +3600,31 @@
       <c r="A148" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B148" s="4" t="s">
-        <v>19</v>
+      <c r="B148" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D148" s="6"/>
       <c r="E148" s="6" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="2" t="s">
-        <v>155</v>
+      <c r="A149" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F149" s="4"/>
     </row>
@@ -3633,30 +3633,30 @@
         <v>155</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F151" s="4"/>
     </row>
@@ -3665,14 +3665,14 @@
         <v>156</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D152" s="6"/>
       <c r="E152" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F152" s="4"/>
     </row>
@@ -3681,14 +3681,14 @@
         <v>156</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F153" s="4"/>
     </row>
@@ -3697,30 +3697,30 @@
         <v>156</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A155" s="3" t="s">
-        <v>157</v>
+      <c r="A155" s="2" t="s">
+        <v>156</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F155" s="4"/>
     </row>
@@ -3729,14 +3729,14 @@
         <v>157</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D156" s="6"/>
       <c r="E156" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F156" s="4"/>
     </row>
@@ -3745,14 +3745,14 @@
         <v>157</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F157" s="4"/>
     </row>
@@ -3761,30 +3761,30 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D158" s="6"/>
       <c r="E158" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F158" s="4"/>
     </row>
     <row r="159" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F159" s="4"/>
     </row>
@@ -3793,30 +3793,30 @@
         <v>158</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D160" s="6"/>
       <c r="E160" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F160" s="4"/>
     </row>
     <row r="161" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F161" s="4"/>
     </row>
@@ -3825,23 +3825,31 @@
         <v>159</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F162" s="4"/>
+    </row>
+    <row r="163" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A163" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="6"/>
+      <c r="E163" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F162" s="4"/>
-    </row>
-    <row r="163" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="6"/>
-      <c r="E163" s="6"/>
       <c r="F163" s="4"/>
     </row>
     <row r="164" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4515,6 +4523,14 @@
       <c r="D247" s="6"/>
       <c r="E247" s="6"/>
       <c r="F247" s="4"/>
+    </row>
+    <row r="248" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A248" s="3"/>
+      <c r="B248" s="3"/>
+      <c r="C248" s="5"/>
+      <c r="D248" s="6"/>
+      <c r="E248" s="6"/>
+      <c r="F248" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034335D0-8935-4D28-9124-0DEEC64DEFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9727DE-A093-42A1-A1CA-A16549412B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="690" windowWidth="28800" windowHeight="15510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4380" yWindow="4245" windowWidth="28395" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="161">
   <si>
     <t>ClassName</t>
   </si>
@@ -825,6 +825,10 @@
   </si>
   <si>
     <t>FuncKaiin_DlgEntry_Idoinfo</t>
+  </si>
+  <si>
+    <t>FuncHikiotoshi</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -3853,19 +3857,35 @@
       <c r="F163" s="4"/>
     </row>
     <row r="164" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
-      <c r="C164" s="5"/>
+      <c r="A164" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D164" s="6"/>
-      <c r="E164" s="6"/>
+      <c r="E164" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="F164" s="4"/>
     </row>
     <row r="165" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
-      <c r="C165" s="5"/>
+      <c r="A165" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D165" s="6"/>
-      <c r="E165" s="6"/>
+      <c r="E165" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F165" s="4"/>
     </row>
     <row r="166" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9727DE-A093-42A1-A1CA-A16549412B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61948C3B-BDF7-47D0-9AD0-A334475F149A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4380" yWindow="4245" windowWidth="28395" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11844" yWindow="19092" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="164">
   <si>
     <t>ClassName</t>
   </si>
@@ -828,6 +828,21 @@
   </si>
   <si>
     <t>FuncHikiotoshi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Edit</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>編集</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncHikiotoshi_DlgEntry</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1232,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F248"/>
+  <dimension ref="A1:F249"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -3864,7 +3879,7 @@
         <v>38</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D164" s="6"/>
       <c r="E164" s="6" t="s">
@@ -3877,39 +3892,63 @@
         <v>160</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F165" s="4"/>
+    </row>
+    <row r="166" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A166" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="6"/>
+      <c r="E166" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F165" s="4"/>
-    </row>
-    <row r="166" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A166" s="3"/>
-      <c r="B166" s="3"/>
-      <c r="C166" s="5"/>
-      <c r="D166" s="6"/>
-      <c r="E166" s="6"/>
       <c r="F166" s="4"/>
     </row>
     <row r="167" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A167" s="3"/>
-      <c r="B167" s="3"/>
-      <c r="C167" s="5"/>
+      <c r="A167" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D167" s="6"/>
-      <c r="E167" s="6"/>
+      <c r="E167" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="F167" s="4"/>
     </row>
     <row r="168" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
-      <c r="C168" s="5"/>
+      <c r="A168" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D168" s="6"/>
-      <c r="E168" s="6"/>
+      <c r="E168" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F168" s="4"/>
     </row>
     <row r="169" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4551,6 +4590,14 @@
       <c r="D248" s="6"/>
       <c r="E248" s="6"/>
       <c r="F248" s="4"/>
+    </row>
+    <row r="249" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A249" s="3"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="5"/>
+      <c r="D249" s="6"/>
+      <c r="E249" s="6"/>
+      <c r="F249" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKaiin\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61948C3B-BDF7-47D0-9AD0-A334475F149A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA0783D-451E-40DA-B8E7-69ACCFFD27FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11844" yWindow="19092" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="705" windowWidth="28800" windowHeight="15495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$147</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="165">
   <si>
     <t>ClassName</t>
   </si>
@@ -843,6 +843,10 @@
   </si>
   <si>
     <t>FuncHikiotoshi_DlgEntry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncOutIryoKikan</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1247,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -3795,31 +3799,31 @@
       <c r="A159" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B159" s="4" t="s">
-        <v>19</v>
+      <c r="B159" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="F159" s="4"/>
     </row>
     <row r="160" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D160" s="6"/>
       <c r="E160" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F160" s="4"/>
     </row>
@@ -3828,30 +3832,30 @@
         <v>158</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F161" s="4"/>
     </row>
     <row r="162" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F162" s="4"/>
     </row>
@@ -3860,30 +3864,30 @@
         <v>159</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D163" s="6"/>
       <c r="E163" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F163" s="4"/>
     </row>
     <row r="164" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>38</v>
+        <v>159</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D164" s="6"/>
       <c r="E164" s="6" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F164" s="4"/>
     </row>
@@ -3892,14 +3896,14 @@
         <v>160</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6" t="s">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="F165" s="4"/>
     </row>
@@ -3908,30 +3912,30 @@
         <v>160</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="D166" s="6"/>
       <c r="E166" s="6" t="s">
-        <v>26</v>
+        <v>162</v>
       </c>
       <c r="F166" s="4"/>
     </row>
     <row r="167" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F167" s="4"/>
     </row>
@@ -3940,39 +3944,63 @@
         <v>163</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D168" s="6"/>
       <c r="E168" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F168" s="4"/>
+    </row>
+    <row r="169" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A169" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="6"/>
+      <c r="E169" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F168" s="4"/>
-    </row>
-    <row r="169" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A169" s="3"/>
-      <c r="B169" s="3"/>
-      <c r="C169" s="5"/>
-      <c r="D169" s="6"/>
-      <c r="E169" s="6"/>
       <c r="F169" s="4"/>
     </row>
     <row r="170" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
-      <c r="C170" s="5"/>
+      <c r="A170" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="D170" s="6"/>
-      <c r="E170" s="6"/>
+      <c r="E170" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="F170" s="4"/>
     </row>
     <row r="171" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
-      <c r="C171" s="5"/>
+      <c r="A171" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D171" s="6"/>
-      <c r="E171" s="6"/>
+      <c r="E171" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F171" s="4"/>
     </row>
     <row r="172" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4598,6 +4626,14 @@
       <c r="D249" s="6"/>
       <c r="E249" s="6"/>
       <c r="F249" s="4"/>
+    </row>
+    <row r="250" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A250" s="3"/>
+      <c r="B250" s="3"/>
+      <c r="C250" s="5"/>
+      <c r="D250" s="6"/>
+      <c r="E250" s="6"/>
+      <c r="F250" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA0783D-451E-40DA-B8E7-69ACCFFD27FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E281B3DA-DCE9-4349-B262-EAC9864C64F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="705" windowWidth="28800" windowHeight="15495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8565" yWindow="2565" windowWidth="28800" windowHeight="13605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$152</definedName>
   </definedNames>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="183">
   <si>
     <t>ClassName</t>
   </si>
@@ -847,6 +847,103 @@
   </si>
   <si>
     <t>FuncOutIryoKikan</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ShowTab1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>情報1表示</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ShowTab2</t>
+  </si>
+  <si>
+    <t>情報2表示</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ShowTab3</t>
+  </si>
+  <si>
+    <t>情報3表示</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>帳票1</t>
+    <rPh sb="0" eb="2">
+      <t>チョウヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>帳票2</t>
+    <rPh sb="0" eb="2">
+      <t>チョウヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>帳票3</t>
+    <rPh sb="0" eb="2">
+      <t>チョウヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>帳票4</t>
+    <rPh sb="0" eb="2">
+      <t>チョウヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>帳票5</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Preview1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Preview2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Preview3</t>
+  </si>
+  <si>
+    <t>Preview4</t>
+  </si>
+  <si>
+    <t>Preview5</t>
+  </si>
+  <si>
+    <t>FuncOutKaihiUchiwakeYear</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncOutKaihiListBank</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1251,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -3493,327 +3590,327 @@
     </row>
     <row r="140" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B140" s="4" t="s">
-        <v>19</v>
+        <v>149</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>176</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6" t="s">
-        <v>26</v>
+        <v>171</v>
       </c>
       <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>11</v>
+        <v>149</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>177</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6" t="s">
-        <v>6</v>
+        <v>172</v>
       </c>
       <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B142" s="4" t="s">
-        <v>7</v>
+        <v>149</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>178</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>8</v>
+        <v>123</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="6" t="s">
-        <v>9</v>
+        <v>173</v>
       </c>
       <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B143" s="4" t="s">
-        <v>11</v>
+        <v>149</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>179</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>13</v>
+        <v>124</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6" t="s">
-        <v>6</v>
+        <v>174</v>
       </c>
       <c r="F143" s="4"/>
     </row>
     <row r="144" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>7</v>
+        <v>149</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="6" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F146" s="4"/>
     </row>
     <row r="147" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F147" s="4"/>
     </row>
     <row r="148" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B148" s="3" t="s">
-        <v>110</v>
+        <v>153</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D148" s="6"/>
       <c r="E148" s="6" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="2" t="s">
-        <v>155</v>
+      <c r="A150" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="2" t="s">
-        <v>155</v>
+      <c r="A151" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="2" t="s">
-        <v>156</v>
+      <c r="A152" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D152" s="6"/>
       <c r="E152" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A153" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B153" s="4" t="s">
-        <v>17</v>
+      <c r="A153" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A154" s="2" t="s">
-        <v>156</v>
+      <c r="A154" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A155" s="2" t="s">
-        <v>156</v>
+      <c r="A155" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F155" s="4"/>
     </row>
     <row r="156" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D156" s="6"/>
       <c r="E156" s="6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F156" s="4"/>
     </row>
     <row r="157" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F157" s="4"/>
     </row>
     <row r="158" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D158" s="6"/>
       <c r="E158" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F158" s="4"/>
     </row>
     <row r="159" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B159" s="3" t="s">
-        <v>110</v>
+        <v>156</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6" t="s">
-        <v>112</v>
+        <v>25</v>
       </c>
       <c r="F159" s="4"/>
     </row>
     <row r="160" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B160" s="4" t="s">
         <v>19</v>
@@ -3829,274 +3926,370 @@
     </row>
     <row r="161" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F161" s="4"/>
     </row>
     <row r="162" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F162" s="4"/>
     </row>
     <row r="163" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D163" s="6"/>
       <c r="E163" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F163" s="4"/>
     </row>
     <row r="164" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B164" s="4" t="s">
-        <v>7</v>
+        <v>157</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="D164" s="6"/>
       <c r="E164" s="6" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="F164" s="4"/>
     </row>
     <row r="165" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>38</v>
+        <v>157</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F165" s="4"/>
     </row>
     <row r="166" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B166" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>124</v>
+        <v>34</v>
       </c>
       <c r="D166" s="6"/>
       <c r="E166" s="6" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F166" s="4"/>
     </row>
     <row r="167" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B167" s="3" t="s">
-        <v>19</v>
+        <v>158</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6" t="s">
-        <v>26</v>
+        <v>168</v>
       </c>
       <c r="F167" s="4"/>
     </row>
     <row r="168" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B168" s="3" t="s">
-        <v>11</v>
+        <v>158</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
       <c r="D168" s="6"/>
       <c r="E168" s="6" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
       <c r="F168" s="4"/>
     </row>
     <row r="169" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B169" s="3" t="s">
-        <v>7</v>
+        <v>158</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F169" s="4"/>
     </row>
     <row r="170" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B170" s="3" t="s">
-        <v>110</v>
+        <v>158</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D170" s="6"/>
       <c r="E170" s="6" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="F170" s="4"/>
     </row>
     <row r="171" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F171" s="4"/>
+    </row>
+    <row r="172" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A172" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="6"/>
+      <c r="E172" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="4"/>
+    </row>
+    <row r="173" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A173" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D173" s="6"/>
+      <c r="E173" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F173" s="4"/>
+    </row>
+    <row r="174" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A174" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D174" s="6"/>
+      <c r="E174" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F174" s="4"/>
+    </row>
+    <row r="175" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A175" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="6"/>
+      <c r="E175" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F171" s="4"/>
-    </row>
-    <row r="172" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
-      <c r="C172" s="5"/>
-      <c r="D172" s="6"/>
-      <c r="E172" s="6"/>
-      <c r="F172" s="4"/>
-    </row>
-    <row r="173" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
-      <c r="C173" s="5"/>
-      <c r="D173" s="6"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="4"/>
-    </row>
-    <row r="174" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
-      <c r="C174" s="5"/>
-      <c r="D174" s="6"/>
-      <c r="E174" s="6"/>
-      <c r="F174" s="4"/>
-    </row>
-    <row r="175" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
-      <c r="C175" s="5"/>
-      <c r="D175" s="6"/>
-      <c r="E175" s="6"/>
       <c r="F175" s="4"/>
     </row>
     <row r="176" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
-      <c r="C176" s="5"/>
+      <c r="A176" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="D176" s="6"/>
-      <c r="E176" s="6"/>
+      <c r="E176" s="6" t="s">
+        <v>6</v>
+      </c>
       <c r="F176" s="4"/>
     </row>
     <row r="177" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
-      <c r="C177" s="5"/>
+      <c r="A177" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D177" s="6"/>
-      <c r="E177" s="6"/>
+      <c r="E177" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F177" s="4"/>
     </row>
     <row r="178" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
-      <c r="C178" s="5"/>
+      <c r="A178" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="D178" s="6"/>
-      <c r="E178" s="6"/>
+      <c r="E178" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="F178" s="4"/>
     </row>
     <row r="179" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
-      <c r="C179" s="5"/>
+      <c r="A179" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D179" s="6"/>
-      <c r="E179" s="6"/>
+      <c r="E179" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F179" s="4"/>
     </row>
     <row r="180" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
-      <c r="C180" s="5"/>
+      <c r="A180" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
+      <c r="E180" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="F180" s="4"/>
     </row>
     <row r="181" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
-      <c r="C181" s="5"/>
+      <c r="A181" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B181" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D181" s="6"/>
-      <c r="E181" s="6"/>
+      <c r="E181" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F181" s="4"/>
     </row>
     <row r="182" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
-      <c r="C182" s="5"/>
+      <c r="A182" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>103</v>
+      </c>
       <c r="D182" s="6"/>
-      <c r="E182" s="6"/>
+      <c r="E182" s="6" t="s">
+        <v>112</v>
+      </c>
       <c r="F182" s="4"/>
     </row>
     <row r="183" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
-      <c r="C183" s="5"/>
+      <c r="A183" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D183" s="6"/>
-      <c r="E183" s="6"/>
+      <c r="E183" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F183" s="4"/>
     </row>
     <row r="184" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4109,7 +4302,7 @@
     </row>
     <row r="185" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
+      <c r="B185" s="4"/>
       <c r="C185" s="5"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
@@ -4635,8 +4828,72 @@
       <c r="E250" s="6"/>
       <c r="F250" s="4"/>
     </row>
+    <row r="251" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A251" s="3"/>
+      <c r="B251" s="3"/>
+      <c r="C251" s="5"/>
+      <c r="D251" s="6"/>
+      <c r="E251" s="6"/>
+      <c r="F251" s="4"/>
+    </row>
+    <row r="252" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A252" s="3"/>
+      <c r="B252" s="3"/>
+      <c r="C252" s="5"/>
+      <c r="D252" s="6"/>
+      <c r="E252" s="6"/>
+      <c r="F252" s="4"/>
+    </row>
+    <row r="253" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A253" s="3"/>
+      <c r="B253" s="3"/>
+      <c r="C253" s="5"/>
+      <c r="D253" s="6"/>
+      <c r="E253" s="6"/>
+      <c r="F253" s="4"/>
+    </row>
+    <row r="254" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A254" s="3"/>
+      <c r="B254" s="3"/>
+      <c r="C254" s="5"/>
+      <c r="D254" s="6"/>
+      <c r="E254" s="6"/>
+      <c r="F254" s="4"/>
+    </row>
+    <row r="255" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A255" s="3"/>
+      <c r="B255" s="3"/>
+      <c r="C255" s="5"/>
+      <c r="D255" s="6"/>
+      <c r="E255" s="6"/>
+      <c r="F255" s="4"/>
+    </row>
+    <row r="256" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A256" s="3"/>
+      <c r="B256" s="3"/>
+      <c r="C256" s="5"/>
+      <c r="D256" s="6"/>
+      <c r="E256" s="6"/>
+      <c r="F256" s="4"/>
+    </row>
+    <row r="257" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A257" s="3"/>
+      <c r="B257" s="3"/>
+      <c r="C257" s="5"/>
+      <c r="D257" s="6"/>
+      <c r="E257" s="6"/>
+      <c r="F257" s="4"/>
+    </row>
+    <row r="258" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A258" s="3"/>
+      <c r="B258" s="3"/>
+      <c r="C258" s="5"/>
+      <c r="D258" s="6"/>
+      <c r="E258" s="6"/>
+      <c r="F258" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F147" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F152" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E281B3DA-DCE9-4349-B262-EAC9864C64F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47E9F78-FC7C-469D-9339-27DB2182C837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8565" yWindow="2565" windowWidth="28800" windowHeight="13605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9225" yWindow="2010" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">AppFuncKey!$A$1:$F$107</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="146">
   <si>
     <t>ClassName</t>
   </si>
@@ -155,30 +155,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>FuncMasterShokumu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncMasterShokumu_DlgEntry</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncMasterTeate</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncMasterTeate_DlgEntry</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncMasterKinmuTanka</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncMasterKinmuTanka_DlgEntry</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>CopyAdd</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -194,10 +170,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>FuncStaff_DlgEntry</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncSelectorDateYM</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -247,113 +219,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>FuncKinmubo</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>AddTeate</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>DeleteTeate</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F5</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>F6</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>AddKyushin</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>EditKyushin</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>DeleteKyushin</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F2</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F3</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F4</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F12</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>休診追加</t>
-    <rPh sb="0" eb="2">
-      <t>キュウシン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>休診訂正</t>
-    <rPh sb="0" eb="2">
-      <t>キュウシン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイセイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>休診削除</t>
-    <rPh sb="0" eb="2">
-      <t>キュウシン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncKnmubo_DlgEntryTeate</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncKnmubo_DlgEntryKyushin</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncMasterGensen</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncMasterBank</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>FuncMasterBank_DlgEntry</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>FuncFixedKyuyo</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Exec</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F11</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -453,10 +327,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ShowTekiyo</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncSelectorBankCode</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -465,30 +335,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>摘要辞書</t>
-    <rPh sb="0" eb="2">
-      <t>テキヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジショ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>摘要選択</t>
-    <rPh sb="0" eb="2">
-      <t>テキヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>センタク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncMasterTekiyo</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -497,55 +343,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>事業手当追加</t>
-    <rPh sb="0" eb="2">
-      <t>ジギョウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テアテ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>事業手当訂正</t>
-    <rPh sb="2" eb="4">
-      <t>テアテ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>テイセイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>事業手当削除</t>
-    <rPh sb="2" eb="4">
-      <t>テアテ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>AddTeateMonth</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>EditTeate</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>EditTeateMonth</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>DeleteTeateMoth</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>F9</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -554,42 +351,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>月度手当追加</t>
-    <rPh sb="0" eb="1">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="1" eb="2">
-      <t>ド</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テアテ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>月度手当訂正</t>
-    <rPh sb="2" eb="4">
-      <t>テアテ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>テイセイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>月度手当削除</t>
-    <rPh sb="2" eb="4">
-      <t>テアテ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サクジョ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>FuncMasterJigyo</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -599,10 +360,6 @@
   </si>
   <si>
     <t>Preview</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>F9</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -643,10 +400,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>FuncStaff</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ExportCSV</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -944,6 +697,48 @@
   </si>
   <si>
     <t>FuncOutKaihiListBank</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>再入会</t>
+    <rPh sb="0" eb="3">
+      <t>サイニュウカイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Rejoin</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>在籍期間表示</t>
+    <rPh sb="0" eb="2">
+      <t>ザイセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ShowZaiseki</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ShowBank</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>銀行情報</t>
+    <rPh sb="0" eb="2">
+      <t>ギンコウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウホウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1348,7 +1143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F258"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -1385,14 +1180,14 @@
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="6" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="F2" s="4"/>
     </row>
@@ -1401,870 +1196,870 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4"/>
     </row>
     <row r="8" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" s="4"/>
     </row>
     <row r="9" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="F9" s="4"/>
     </row>
     <row r="10" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>85</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="F10" s="4"/>
     </row>
     <row r="11" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F11" s="4"/>
     </row>
     <row r="12" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F13" s="4"/>
     </row>
     <row r="14" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F14" s="4"/>
     </row>
     <row r="15" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F15" s="4"/>
     </row>
     <row r="16" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="F16" s="4"/>
     </row>
     <row r="17" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F17" s="4"/>
     </row>
     <row r="18" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F20" s="4"/>
     </row>
     <row r="21" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="F21" s="4"/>
     </row>
     <row r="22" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F25" s="4"/>
     </row>
     <row r="26" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
-        <v>119</v>
+        <v>49</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F26" s="4"/>
     </row>
     <row r="27" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F27" s="4"/>
     </row>
     <row r="28" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>7</v>
+        <v>50</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D28" s="6"/>
-      <c r="E28" s="6" t="s">
-        <v>9</v>
+      <c r="E28" s="4" t="s">
+        <v>43</v>
       </c>
       <c r="F28" s="4"/>
     </row>
     <row r="29" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F29" s="4"/>
     </row>
     <row r="30" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>11</v>
+        <v>61</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="F31" s="4"/>
     </row>
     <row r="32" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="F32" s="4"/>
     </row>
     <row r="33" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="F33" s="4"/>
     </row>
     <row r="34" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>58</v>
       </c>
       <c r="F34" s="4"/>
     </row>
     <row r="35" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="3" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="F35" s="4"/>
     </row>
     <row r="36" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="F36" s="4"/>
     </row>
     <row r="37" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
       <c r="F37" s="4"/>
     </row>
     <row r="38" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="F38" s="4"/>
     </row>
     <row r="39" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="F39" s="4"/>
     </row>
     <row r="40" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="F40" s="4"/>
     </row>
     <row r="41" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>100</v>
+        <v>7</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="F41" s="4"/>
     </row>
     <row r="42" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>49</v>
+        <v>67</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>123</v>
+        <v>20</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6" t="s">
-        <v>98</v>
+        <v>23</v>
       </c>
       <c r="F42" s="4"/>
     </row>
     <row r="43" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6" t="s">
-        <v>105</v>
+        <v>24</v>
       </c>
       <c r="F43" s="4"/>
     </row>
     <row r="44" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="F44" s="4"/>
     </row>
     <row r="45" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>102</v>
+        <v>67</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="F45" s="4"/>
     </row>
     <row r="46" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F46" s="4"/>
     </row>
     <row r="47" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F47" s="4"/>
     </row>
     <row r="48" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>7</v>
+        <v>71</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="F48" s="4"/>
     </row>
     <row r="49" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>88</v>
+        <v>71</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="F49" s="4"/>
     </row>
     <row r="50" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>11</v>
+        <v>74</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="F50" s="4"/>
     </row>
     <row r="51" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>7</v>
+        <v>74</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F51" s="4"/>
     </row>
     <row r="52" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>11</v>
+        <v>75</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="F52" s="4"/>
     </row>
     <row r="53" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>7</v>
+        <v>75</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="F53" s="4"/>
     </row>
     <row r="54" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>16</v>
+        <v>75</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F54" s="4"/>
     </row>
     <row r="55" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F55" s="4"/>
     </row>
     <row r="56" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>18</v>
+        <v>76</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="F56" s="4"/>
     </row>
     <row r="57" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C57" s="5" t="s">
@@ -2278,215 +2073,215 @@
     </row>
     <row r="58" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="F58" s="4"/>
     </row>
     <row r="59" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F59" s="4"/>
     </row>
     <row r="60" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F60" s="4"/>
     </row>
     <row r="61" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6" t="s">
-        <v>112</v>
+        <v>9</v>
       </c>
       <c r="F61" s="4"/>
     </row>
     <row r="62" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="D62" s="6"/>
-      <c r="E62" s="4" t="s">
-        <v>70</v>
+      <c r="E62" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C63" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>16</v>
+        <v>90</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>17</v>
+        <v>90</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F66" s="4"/>
     </row>
     <row r="67" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F67" s="4"/>
     </row>
     <row r="68" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6" t="s">
-        <v>74</v>
+        <v>25</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F69" s="4"/>
     </row>
     <row r="70" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>7</v>
+        <v>93</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="F70" s="4"/>
     </row>
     <row r="71" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>11</v>
@@ -2502,7 +2297,7 @@
     </row>
     <row r="72" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="B72" s="4" t="s">
         <v>7</v>
@@ -2518,487 +2313,487 @@
     </row>
     <row r="73" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>13</v>
       </c>
       <c r="D73" s="6"/>
-      <c r="E73" s="4" t="s">
-        <v>70</v>
+      <c r="E73" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="F73" s="4"/>
     </row>
     <row r="74" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F74" s="4"/>
     </row>
     <row r="75" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>86</v>
+        <v>96</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="F77" s="4"/>
     </row>
     <row r="78" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>86</v>
+        <v>98</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>100</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="F78" s="4"/>
     </row>
     <row r="79" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="F79" s="4"/>
     </row>
     <row r="80" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>18</v>
+        <v>101</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F83" s="4"/>
     </row>
     <row r="84" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="3" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F84" s="4"/>
     </row>
     <row r="85" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F85" s="4"/>
     </row>
     <row r="86" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="6" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F86" s="4"/>
     </row>
     <row r="87" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F87" s="4"/>
     </row>
     <row r="88" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F88" s="4"/>
     </row>
     <row r="89" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F89" s="4"/>
     </row>
     <row r="90" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F90" s="4"/>
     </row>
     <row r="91" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F91" s="4"/>
     </row>
     <row r="92" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="6" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F92" s="4"/>
     </row>
     <row r="93" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6" t="s">
-        <v>115</v>
+        <v>24</v>
       </c>
       <c r="F93" s="4"/>
     </row>
     <row r="94" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>19</v>
+        <v>106</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="F94" s="4"/>
     </row>
     <row r="95" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F95" s="4"/>
     </row>
     <row r="96" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>19</v>
+        <v>134</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="6" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="F96" s="4"/>
     </row>
     <row r="97" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="6" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="F97" s="4"/>
     </row>
     <row r="98" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F98" s="4"/>
     </row>
     <row r="99" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="F99" s="4"/>
     </row>
     <row r="100" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="6" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="F100" s="4"/>
     </row>
     <row r="101" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="6" t="s">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="F101" s="4"/>
     </row>
     <row r="102" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>19</v>
+        <v>109</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F102" s="4"/>
     </row>
     <row r="103" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="3" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>11</v>
@@ -3014,7 +2809,7 @@
     </row>
     <row r="104" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="3" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>7</v>
@@ -3030,253 +2825,253 @@
     </row>
     <row r="105" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F105" s="4"/>
     </row>
     <row r="106" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F106" s="4"/>
     </row>
     <row r="107" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B107" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="F107" s="4"/>
     </row>
     <row r="108" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>7</v>
+        <v>111</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="F108" s="4"/>
     </row>
     <row r="109" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B109" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="6" t="s">
-        <v>112</v>
+        <v>26</v>
       </c>
       <c r="F109" s="4"/>
     </row>
     <row r="110" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B110" s="3" t="s">
-        <v>19</v>
+        <v>112</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F110" s="4"/>
     </row>
     <row r="111" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="3" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F111" s="4"/>
     </row>
     <row r="112" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F112" s="4"/>
     </row>
     <row r="113" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F113" s="4"/>
     </row>
     <row r="114" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F114" s="4"/>
     </row>
     <row r="115" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="3" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6" t="s">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="F115" s="4"/>
     </row>
     <row r="116" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F116" s="4"/>
     </row>
     <row r="117" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="3" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F117" s="4"/>
     </row>
     <row r="118" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B118" s="3" t="s">
-        <v>38</v>
+        <v>114</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F118" s="4"/>
     </row>
     <row r="119" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="3" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F119" s="4"/>
     </row>
     <row r="120" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B120" s="3" t="s">
-        <v>38</v>
+        <v>114</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>141</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="6" t="s">
@@ -3286,135 +3081,135 @@
     </row>
     <row r="121" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="3" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F121" s="4"/>
     </row>
     <row r="122" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="3" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F122" s="4"/>
     </row>
     <row r="123" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B123" s="3" t="s">
-        <v>143</v>
+        <v>114</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>103</v>
+        <v>8</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="F123" s="4"/>
     </row>
     <row r="124" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B124" s="3" t="s">
-        <v>19</v>
+        <v>115</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="F124" s="4"/>
     </row>
     <row r="125" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="3" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6" t="s">
-        <v>23</v>
+        <v>125</v>
       </c>
       <c r="F125" s="4"/>
     </row>
     <row r="126" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="3" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="F126" s="4"/>
     </row>
     <row r="127" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="3" t="s">
-        <v>144</v>
+        <v>115</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="F127" s="4"/>
     </row>
     <row r="128" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B128" s="3" t="s">
-        <v>19</v>
+        <v>115</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="6" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F128" s="4"/>
     </row>
     <row r="129" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="3" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>11</v>
@@ -3430,7 +3225,7 @@
     </row>
     <row r="130" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="3" t="s">
-        <v>145</v>
+        <v>116</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>7</v>
@@ -3446,850 +3241,514 @@
     </row>
     <row r="131" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B131" s="4" t="s">
-        <v>16</v>
+        <v>117</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F131" s="4"/>
     </row>
     <row r="132" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B132" s="4" t="s">
-        <v>17</v>
+        <v>117</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="6" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="F132" s="4"/>
     </row>
     <row r="133" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B133" s="4" t="s">
-        <v>18</v>
+        <v>117</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>19</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F133" s="4"/>
     </row>
     <row r="134" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B134" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F134" s="4"/>
     </row>
     <row r="135" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>11</v>
+        <v>120</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>7</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F135" s="4"/>
     </row>
     <row r="136" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B136" s="4" t="s">
-        <v>7</v>
+        <v>121</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6" t="s">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="F136" s="4"/>
     </row>
     <row r="137" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="3" t="s">
-        <v>150</v>
+        <v>121</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F137" s="4"/>
     </row>
     <row r="138" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B138" s="4" t="s">
-        <v>17</v>
+        <v>138</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="F138" s="4"/>
     </row>
     <row r="139" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F139" s="4"/>
     </row>
     <row r="140" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B141" s="3" t="s">
-        <v>177</v>
+        <v>139</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
       <c r="F141" s="4"/>
     </row>
     <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B142" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="5"/>
       <c r="D142" s="6"/>
-      <c r="E142" s="6" t="s">
-        <v>173</v>
-      </c>
+      <c r="E142" s="6"/>
       <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A143" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B143" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>124</v>
-      </c>
+      <c r="A143" s="3"/>
+      <c r="B143" s="4"/>
+      <c r="C143" s="5"/>
       <c r="D143" s="6"/>
-      <c r="E143" s="6" t="s">
-        <v>174</v>
-      </c>
+      <c r="E143" s="6"/>
       <c r="F143" s="4"/>
     </row>
     <row r="144" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A144" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="B144" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="5"/>
       <c r="D144" s="6"/>
-      <c r="E144" s="6" t="s">
-        <v>175</v>
-      </c>
+      <c r="E144" s="6"/>
       <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A145" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="5"/>
       <c r="D145" s="6"/>
-      <c r="E145" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E145" s="6"/>
       <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A146" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B146" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="5"/>
       <c r="D146" s="6"/>
-      <c r="E146" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="E146" s="6"/>
       <c r="F146" s="4"/>
     </row>
     <row r="147" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A147" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="5"/>
       <c r="D147" s="6"/>
-      <c r="E147" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E147" s="6"/>
       <c r="F147" s="4"/>
     </row>
     <row r="148" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A148" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B148" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="5"/>
       <c r="D148" s="6"/>
-      <c r="E148" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="E148" s="6"/>
       <c r="F148" s="4"/>
     </row>
     <row r="149" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A149" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B149" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="5"/>
       <c r="D149" s="6"/>
-      <c r="E149" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E149" s="6"/>
       <c r="F149" s="4"/>
     </row>
     <row r="150" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A150" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="5"/>
       <c r="D150" s="6"/>
-      <c r="E150" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="E150" s="6"/>
       <c r="F150" s="4"/>
     </row>
     <row r="151" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A151" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B151" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="5"/>
       <c r="D151" s="6"/>
-      <c r="E151" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="E151" s="6"/>
       <c r="F151" s="4"/>
     </row>
     <row r="152" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A152" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B152" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="5"/>
       <c r="D152" s="6"/>
-      <c r="E152" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="E152" s="6"/>
       <c r="F152" s="4"/>
     </row>
     <row r="153" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A153" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="5"/>
       <c r="D153" s="6"/>
-      <c r="E153" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="E153" s="6"/>
       <c r="F153" s="4"/>
     </row>
     <row r="154" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A154" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B154" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="5"/>
       <c r="D154" s="6"/>
-      <c r="E154" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E154" s="6"/>
       <c r="F154" s="4"/>
     </row>
     <row r="155" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A155" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B155" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="5"/>
       <c r="D155" s="6"/>
-      <c r="E155" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="E155" s="6"/>
       <c r="F155" s="4"/>
     </row>
     <row r="156" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A156" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B156" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="5"/>
       <c r="D156" s="6"/>
-      <c r="E156" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E156" s="6"/>
       <c r="F156" s="4"/>
     </row>
     <row r="157" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A157" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B157" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="5"/>
       <c r="D157" s="6"/>
-      <c r="E157" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="E157" s="6"/>
       <c r="F157" s="4"/>
     </row>
     <row r="158" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A158" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B158" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="5"/>
       <c r="D158" s="6"/>
-      <c r="E158" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="E158" s="6"/>
       <c r="F158" s="4"/>
     </row>
     <row r="159" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A159" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="5"/>
       <c r="D159" s="6"/>
-      <c r="E159" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="E159" s="6"/>
       <c r="F159" s="4"/>
     </row>
     <row r="160" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A160" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="B160" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="5"/>
       <c r="D160" s="6"/>
-      <c r="E160" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E160" s="6"/>
       <c r="F160" s="4"/>
     </row>
     <row r="161" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A161" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B161" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="5"/>
       <c r="D161" s="6"/>
-      <c r="E161" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="E161" s="6"/>
       <c r="F161" s="4"/>
     </row>
     <row r="162" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A162" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B162" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="5"/>
       <c r="D162" s="6"/>
-      <c r="E162" s="6" t="s">
-        <v>24</v>
-      </c>
+      <c r="E162" s="6"/>
       <c r="F162" s="4"/>
     </row>
     <row r="163" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A163" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B163" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="5"/>
       <c r="D163" s="6"/>
-      <c r="E163" s="6" t="s">
-        <v>25</v>
-      </c>
+      <c r="E163" s="6"/>
       <c r="F163" s="4"/>
     </row>
     <row r="164" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A164" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B164" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="5"/>
       <c r="D164" s="6"/>
-      <c r="E164" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="E164" s="6"/>
       <c r="F164" s="4"/>
     </row>
     <row r="165" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A165" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B165" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="5"/>
       <c r="D165" s="6"/>
-      <c r="E165" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E165" s="6"/>
       <c r="F165" s="4"/>
     </row>
     <row r="166" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A166" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B166" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="5"/>
       <c r="D166" s="6"/>
-      <c r="E166" s="6" t="s">
-        <v>166</v>
-      </c>
+      <c r="E166" s="6"/>
       <c r="F166" s="4"/>
     </row>
     <row r="167" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A167" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B167" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>51</v>
-      </c>
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="5"/>
       <c r="D167" s="6"/>
-      <c r="E167" s="6" t="s">
-        <v>168</v>
-      </c>
+      <c r="E167" s="6"/>
       <c r="F167" s="4"/>
     </row>
     <row r="168" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A168" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B168" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>123</v>
-      </c>
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="5"/>
       <c r="D168" s="6"/>
-      <c r="E168" s="6" t="s">
-        <v>170</v>
-      </c>
+      <c r="E168" s="6"/>
       <c r="F168" s="4"/>
     </row>
     <row r="169" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A169" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B169" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C169" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="5"/>
       <c r="D169" s="6"/>
-      <c r="E169" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="E169" s="6"/>
       <c r="F169" s="4"/>
     </row>
     <row r="170" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A170" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B170" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C170" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="5"/>
       <c r="D170" s="6"/>
-      <c r="E170" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E170" s="6"/>
       <c r="F170" s="4"/>
     </row>
     <row r="171" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A171" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B171" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C171" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="5"/>
       <c r="D171" s="6"/>
-      <c r="E171" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="E171" s="6"/>
       <c r="F171" s="4"/>
     </row>
     <row r="172" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A172" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B172" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C172" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="5"/>
       <c r="D172" s="6"/>
-      <c r="E172" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E172" s="6"/>
       <c r="F172" s="4"/>
     </row>
     <row r="173" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A173" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B173" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C173" s="5" t="s">
-        <v>34</v>
-      </c>
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="5"/>
       <c r="D173" s="6"/>
-      <c r="E173" s="6" t="s">
-        <v>70</v>
-      </c>
+      <c r="E173" s="6"/>
       <c r="F173" s="4"/>
     </row>
     <row r="174" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A174" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B174" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>124</v>
-      </c>
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="5"/>
       <c r="D174" s="6"/>
-      <c r="E174" s="6" t="s">
-        <v>162</v>
-      </c>
+      <c r="E174" s="6"/>
       <c r="F174" s="4"/>
     </row>
     <row r="175" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A175" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="B175" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="5"/>
       <c r="D175" s="6"/>
-      <c r="E175" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E175" s="6"/>
       <c r="F175" s="4"/>
     </row>
     <row r="176" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A176" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B176" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="5"/>
       <c r="D176" s="6"/>
-      <c r="E176" s="6" t="s">
-        <v>6</v>
-      </c>
+      <c r="E176" s="6"/>
       <c r="F176" s="4"/>
     </row>
     <row r="177" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A177" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B177" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C177" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="5"/>
       <c r="D177" s="6"/>
-      <c r="E177" s="6" t="s">
-        <v>9</v>
-      </c>
+      <c r="E177" s="6"/>
       <c r="F177" s="4"/>
     </row>
     <row r="178" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A178" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B178" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="5"/>
       <c r="D178" s="6"/>
-      <c r="E178" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="E178" s="6"/>
       <c r="F178" s="4"/>
     </row>
     <row r="179" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A179" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B179" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="5"/>
       <c r="D179" s="6"/>
-      <c r="E179" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E179" s="6"/>
       <c r="F179" s="4"/>
     </row>
     <row r="180" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A180" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B180" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="5"/>
       <c r="D180" s="6"/>
-      <c r="E180" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="E180" s="6"/>
       <c r="F180" s="4"/>
     </row>
     <row r="181" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A181" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="5"/>
       <c r="D181" s="6"/>
-      <c r="E181" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E181" s="6"/>
       <c r="F181" s="4"/>
     </row>
     <row r="182" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A182" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B182" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>103</v>
-      </c>
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="5"/>
       <c r="D182" s="6"/>
-      <c r="E182" s="6" t="s">
-        <v>112</v>
-      </c>
+      <c r="E182" s="6"/>
       <c r="F182" s="4"/>
     </row>
     <row r="183" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A183" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="B183" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>8</v>
-      </c>
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="5"/>
       <c r="D183" s="6"/>
-      <c r="E183" s="6" t="s">
-        <v>26</v>
-      </c>
+      <c r="E183" s="6"/>
       <c r="F183" s="4"/>
     </row>
     <row r="184" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4302,7 +3761,7 @@
     </row>
     <row r="185" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A185" s="3"/>
-      <c r="B185" s="4"/>
+      <c r="B185" s="3"/>
       <c r="C185" s="5"/>
       <c r="D185" s="6"/>
       <c r="E185" s="6"/>
@@ -4556,344 +4015,8 @@
       <c r="E216" s="6"/>
       <c r="F216" s="4"/>
     </row>
-    <row r="217" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A217" s="3"/>
-      <c r="B217" s="3"/>
-      <c r="C217" s="5"/>
-      <c r="D217" s="6"/>
-      <c r="E217" s="6"/>
-      <c r="F217" s="4"/>
-    </row>
-    <row r="218" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A218" s="3"/>
-      <c r="B218" s="3"/>
-      <c r="C218" s="5"/>
-      <c r="D218" s="6"/>
-      <c r="E218" s="6"/>
-      <c r="F218" s="4"/>
-    </row>
-    <row r="219" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A219" s="3"/>
-      <c r="B219" s="3"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="6"/>
-      <c r="E219" s="6"/>
-      <c r="F219" s="4"/>
-    </row>
-    <row r="220" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A220" s="3"/>
-      <c r="B220" s="3"/>
-      <c r="C220" s="5"/>
-      <c r="D220" s="6"/>
-      <c r="E220" s="6"/>
-      <c r="F220" s="4"/>
-    </row>
-    <row r="221" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A221" s="3"/>
-      <c r="B221" s="3"/>
-      <c r="C221" s="5"/>
-      <c r="D221" s="6"/>
-      <c r="E221" s="6"/>
-      <c r="F221" s="4"/>
-    </row>
-    <row r="222" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A222" s="3"/>
-      <c r="B222" s="3"/>
-      <c r="C222" s="5"/>
-      <c r="D222" s="6"/>
-      <c r="E222" s="6"/>
-      <c r="F222" s="4"/>
-    </row>
-    <row r="223" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A223" s="3"/>
-      <c r="B223" s="3"/>
-      <c r="C223" s="5"/>
-      <c r="D223" s="6"/>
-      <c r="E223" s="6"/>
-      <c r="F223" s="4"/>
-    </row>
-    <row r="224" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A224" s="3"/>
-      <c r="B224" s="3"/>
-      <c r="C224" s="5"/>
-      <c r="D224" s="6"/>
-      <c r="E224" s="6"/>
-      <c r="F224" s="4"/>
-    </row>
-    <row r="225" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A225" s="3"/>
-      <c r="B225" s="3"/>
-      <c r="C225" s="5"/>
-      <c r="D225" s="6"/>
-      <c r="E225" s="6"/>
-      <c r="F225" s="4"/>
-    </row>
-    <row r="226" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A226" s="3"/>
-      <c r="B226" s="3"/>
-      <c r="C226" s="5"/>
-      <c r="D226" s="6"/>
-      <c r="E226" s="6"/>
-      <c r="F226" s="4"/>
-    </row>
-    <row r="227" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A227" s="3"/>
-      <c r="B227" s="3"/>
-      <c r="C227" s="5"/>
-      <c r="D227" s="6"/>
-      <c r="E227" s="6"/>
-      <c r="F227" s="4"/>
-    </row>
-    <row r="228" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A228" s="3"/>
-      <c r="B228" s="3"/>
-      <c r="C228" s="5"/>
-      <c r="D228" s="6"/>
-      <c r="E228" s="6"/>
-      <c r="F228" s="4"/>
-    </row>
-    <row r="229" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A229" s="3"/>
-      <c r="B229" s="3"/>
-      <c r="C229" s="5"/>
-      <c r="D229" s="6"/>
-      <c r="E229" s="6"/>
-      <c r="F229" s="4"/>
-    </row>
-    <row r="230" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A230" s="3"/>
-      <c r="B230" s="3"/>
-      <c r="C230" s="5"/>
-      <c r="D230" s="6"/>
-      <c r="E230" s="6"/>
-      <c r="F230" s="4"/>
-    </row>
-    <row r="231" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A231" s="3"/>
-      <c r="B231" s="3"/>
-      <c r="C231" s="5"/>
-      <c r="D231" s="6"/>
-      <c r="E231" s="6"/>
-      <c r="F231" s="4"/>
-    </row>
-    <row r="232" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A232" s="3"/>
-      <c r="B232" s="3"/>
-      <c r="C232" s="5"/>
-      <c r="D232" s="6"/>
-      <c r="E232" s="6"/>
-      <c r="F232" s="4"/>
-    </row>
-    <row r="233" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A233" s="3"/>
-      <c r="B233" s="3"/>
-      <c r="C233" s="5"/>
-      <c r="D233" s="6"/>
-      <c r="E233" s="6"/>
-      <c r="F233" s="4"/>
-    </row>
-    <row r="234" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A234" s="3"/>
-      <c r="B234" s="3"/>
-      <c r="C234" s="5"/>
-      <c r="D234" s="6"/>
-      <c r="E234" s="6"/>
-      <c r="F234" s="4"/>
-    </row>
-    <row r="235" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A235" s="3"/>
-      <c r="B235" s="3"/>
-      <c r="C235" s="5"/>
-      <c r="D235" s="6"/>
-      <c r="E235" s="6"/>
-      <c r="F235" s="4"/>
-    </row>
-    <row r="236" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A236" s="3"/>
-      <c r="B236" s="3"/>
-      <c r="C236" s="5"/>
-      <c r="D236" s="6"/>
-      <c r="E236" s="6"/>
-      <c r="F236" s="4"/>
-    </row>
-    <row r="237" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A237" s="3"/>
-      <c r="B237" s="3"/>
-      <c r="C237" s="5"/>
-      <c r="D237" s="6"/>
-      <c r="E237" s="6"/>
-      <c r="F237" s="4"/>
-    </row>
-    <row r="238" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A238" s="3"/>
-      <c r="B238" s="3"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="6"/>
-      <c r="E238" s="6"/>
-      <c r="F238" s="4"/>
-    </row>
-    <row r="239" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A239" s="3"/>
-      <c r="B239" s="3"/>
-      <c r="C239" s="5"/>
-      <c r="D239" s="6"/>
-      <c r="E239" s="6"/>
-      <c r="F239" s="4"/>
-    </row>
-    <row r="240" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A240" s="3"/>
-      <c r="B240" s="3"/>
-      <c r="C240" s="5"/>
-      <c r="D240" s="6"/>
-      <c r="E240" s="6"/>
-      <c r="F240" s="4"/>
-    </row>
-    <row r="241" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A241" s="3"/>
-      <c r="B241" s="3"/>
-      <c r="C241" s="5"/>
-      <c r="D241" s="6"/>
-      <c r="E241" s="6"/>
-      <c r="F241" s="4"/>
-    </row>
-    <row r="242" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A242" s="3"/>
-      <c r="B242" s="3"/>
-      <c r="C242" s="5"/>
-      <c r="D242" s="6"/>
-      <c r="E242" s="6"/>
-      <c r="F242" s="4"/>
-    </row>
-    <row r="243" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A243" s="3"/>
-      <c r="B243" s="3"/>
-      <c r="C243" s="5"/>
-      <c r="D243" s="6"/>
-      <c r="E243" s="6"/>
-      <c r="F243" s="4"/>
-    </row>
-    <row r="244" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A244" s="3"/>
-      <c r="B244" s="3"/>
-      <c r="C244" s="5"/>
-      <c r="D244" s="6"/>
-      <c r="E244" s="6"/>
-      <c r="F244" s="4"/>
-    </row>
-    <row r="245" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A245" s="3"/>
-      <c r="B245" s="3"/>
-      <c r="C245" s="5"/>
-      <c r="D245" s="6"/>
-      <c r="E245" s="6"/>
-      <c r="F245" s="4"/>
-    </row>
-    <row r="246" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A246" s="3"/>
-      <c r="B246" s="3"/>
-      <c r="C246" s="5"/>
-      <c r="D246" s="6"/>
-      <c r="E246" s="6"/>
-      <c r="F246" s="4"/>
-    </row>
-    <row r="247" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A247" s="3"/>
-      <c r="B247" s="3"/>
-      <c r="C247" s="5"/>
-      <c r="D247" s="6"/>
-      <c r="E247" s="6"/>
-      <c r="F247" s="4"/>
-    </row>
-    <row r="248" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A248" s="3"/>
-      <c r="B248" s="3"/>
-      <c r="C248" s="5"/>
-      <c r="D248" s="6"/>
-      <c r="E248" s="6"/>
-      <c r="F248" s="4"/>
-    </row>
-    <row r="249" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A249" s="3"/>
-      <c r="B249" s="3"/>
-      <c r="C249" s="5"/>
-      <c r="D249" s="6"/>
-      <c r="E249" s="6"/>
-      <c r="F249" s="4"/>
-    </row>
-    <row r="250" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A250" s="3"/>
-      <c r="B250" s="3"/>
-      <c r="C250" s="5"/>
-      <c r="D250" s="6"/>
-      <c r="E250" s="6"/>
-      <c r="F250" s="4"/>
-    </row>
-    <row r="251" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A251" s="3"/>
-      <c r="B251" s="3"/>
-      <c r="C251" s="5"/>
-      <c r="D251" s="6"/>
-      <c r="E251" s="6"/>
-      <c r="F251" s="4"/>
-    </row>
-    <row r="252" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A252" s="3"/>
-      <c r="B252" s="3"/>
-      <c r="C252" s="5"/>
-      <c r="D252" s="6"/>
-      <c r="E252" s="6"/>
-      <c r="F252" s="4"/>
-    </row>
-    <row r="253" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A253" s="3"/>
-      <c r="B253" s="3"/>
-      <c r="C253" s="5"/>
-      <c r="D253" s="6"/>
-      <c r="E253" s="6"/>
-      <c r="F253" s="4"/>
-    </row>
-    <row r="254" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A254" s="3"/>
-      <c r="B254" s="3"/>
-      <c r="C254" s="5"/>
-      <c r="D254" s="6"/>
-      <c r="E254" s="6"/>
-      <c r="F254" s="4"/>
-    </row>
-    <row r="255" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A255" s="3"/>
-      <c r="B255" s="3"/>
-      <c r="C255" s="5"/>
-      <c r="D255" s="6"/>
-      <c r="E255" s="6"/>
-      <c r="F255" s="4"/>
-    </row>
-    <row r="256" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A256" s="3"/>
-      <c r="B256" s="3"/>
-      <c r="C256" s="5"/>
-      <c r="D256" s="6"/>
-      <c r="E256" s="6"/>
-      <c r="F256" s="4"/>
-    </row>
-    <row r="257" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A257" s="3"/>
-      <c r="B257" s="3"/>
-      <c r="C257" s="5"/>
-      <c r="D257" s="6"/>
-      <c r="E257" s="6"/>
-      <c r="F257" s="4"/>
-    </row>
-    <row r="258" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A258" s="3"/>
-      <c r="B258" s="3"/>
-      <c r="C258" s="5"/>
-      <c r="D258" s="6"/>
-      <c r="E258" s="6"/>
-      <c r="F258" s="4"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F152" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F107" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="1200" r:id="rId1"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\client\DotNet4.6\Ishikai\FMKaiin\_doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A47E9F78-FC7C-469D-9339-27DB2182C837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3D0DFC-2DB8-4EB5-996A-04FC1C862BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9225" yWindow="2010" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10875" yWindow="3900" windowWidth="43200" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AppFuncKey" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="148">
   <si>
     <t>ClassName</t>
   </si>
@@ -739,6 +739,20 @@
     <rPh sb="2" eb="4">
       <t>ジョウホウ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>個別再作成</t>
+    <rPh sb="0" eb="2">
+      <t>コベツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>サイサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ReMake</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1143,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F216"/>
+  <dimension ref="A1:F219"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.125" style="2" customWidth="1"/>
@@ -3260,14 +3274,14 @@
         <v>117</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="6" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="F132" s="4"/>
     </row>
@@ -3276,30 +3290,30 @@
         <v>117</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>19</v>
+        <v>118</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="F133" s="4"/>
     </row>
     <row r="134" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="6" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="F134" s="4"/>
     </row>
@@ -3308,135 +3322,159 @@
         <v>120</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F135" s="4"/>
     </row>
     <row r="136" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="F136" s="4"/>
     </row>
     <row r="137" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>19</v>
+        <v>120</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="F137" s="4"/>
     </row>
     <row r="138" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>69</v>
+        <v>7</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="F138" s="4"/>
     </row>
     <row r="139" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B139" s="4" t="s">
-        <v>19</v>
+        <v>121</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="F139" s="4"/>
     </row>
     <row r="140" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>69</v>
+        <v>121</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F140" s="4"/>
     </row>
     <row r="141" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B141" s="4" t="s">
-        <v>19</v>
+        <v>138</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F141" s="4"/>
+    </row>
+    <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A142" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="6"/>
+      <c r="E142" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F141" s="4"/>
-    </row>
-    <row r="142" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="5"/>
-      <c r="D142" s="6"/>
-      <c r="E142" s="6"/>
       <c r="F142" s="4"/>
     </row>
     <row r="143" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A143" s="3"/>
-      <c r="B143" s="4"/>
-      <c r="C143" s="5"/>
+      <c r="A143" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>65</v>
+      </c>
       <c r="D143" s="6"/>
-      <c r="E143" s="6"/>
+      <c r="E143" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="F143" s="4"/>
     </row>
     <row r="144" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
-      <c r="C144" s="5"/>
+      <c r="A144" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D144" s="6"/>
-      <c r="E144" s="6"/>
+      <c r="E144" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -3449,7 +3487,7 @@
     </row>
     <row r="146" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
+      <c r="B146" s="4"/>
       <c r="C146" s="5"/>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
@@ -4014,6 +4052,30 @@
       <c r="D216" s="6"/>
       <c r="E216" s="6"/>
       <c r="F216" s="4"/>
+    </row>
+    <row r="217" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A217" s="3"/>
+      <c r="B217" s="3"/>
+      <c r="C217" s="5"/>
+      <c r="D217" s="6"/>
+      <c r="E217" s="6"/>
+      <c r="F217" s="4"/>
+    </row>
+    <row r="218" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A218" s="3"/>
+      <c r="B218" s="3"/>
+      <c r="C218" s="5"/>
+      <c r="D218" s="6"/>
+      <c r="E218" s="6"/>
+      <c r="F218" s="4"/>
+    </row>
+    <row r="219" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A219" s="3"/>
+      <c r="B219" s="3"/>
+      <c r="C219" s="5"/>
+      <c r="D219" s="6"/>
+      <c r="E219" s="6"/>
+      <c r="F219" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F107" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/_doc/AppFuncKey.xlsx
+++ b/_doc/AppFuncKey.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\client\DotNet4.6_YMGLib5\FujisawaIshikai\FMKaiin\_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC3D0DFC-2DB8-4EB5-996A-04FC1C862BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{048C223D-D529-4D3E-A880-E0479B7FD544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10875" yWindow="3900" windowWidth="43200" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="149">
   <si>
     <t>ClassName</t>
   </si>
@@ -753,6 +753,10 @@
   </si>
   <si>
     <t>ReMake</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>FuncKaiin_DlgHistory</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3478,11 +3482,19 @@
       <c r="F144" s="4"/>
     </row>
     <row r="145" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
-      <c r="C145" s="5"/>
+      <c r="A145" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="D145" s="6"/>
-      <c r="E145" s="6"/>
+      <c r="E145" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="F145" s="4"/>
     </row>
     <row r="146" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.15">
